--- a/output/tables/mi_vif_pooled_summary.xlsx
+++ b/output/tables/mi_vif_pooled_summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -406,16 +406,16 @@
         <v>50</v>
       </c>
       <c r="D2">
-        <v>1.251866557668387</v>
+        <v>1.260415814655188</v>
       </c>
       <c r="E2">
-        <v>1.251354975797365</v>
+        <v>1.257568739953705</v>
       </c>
       <c r="F2">
-        <v>1.214685975733464</v>
+        <v>1.222787652950922</v>
       </c>
       <c r="G2">
-        <v>1.300394083154973</v>
+        <v>1.30413030383231</v>
       </c>
     </row>
     <row r="3">
@@ -433,16 +433,16 @@
         <v>50</v>
       </c>
       <c r="D3">
-        <v>1.607277255869362</v>
+        <v>1.628922881641169</v>
       </c>
       <c r="E3">
-        <v>1.601244812093376</v>
+        <v>1.614663584321272</v>
       </c>
       <c r="F3">
-        <v>1.467179122618699</v>
+        <v>1.462128333099233</v>
       </c>
       <c r="G3">
-        <v>1.851852028382008</v>
+        <v>1.893277150903137</v>
       </c>
     </row>
     <row r="4">
@@ -460,16 +460,16 @@
         <v>50</v>
       </c>
       <c r="D4">
-        <v>1.59424141820716</v>
+        <v>1.688772813114878</v>
       </c>
       <c r="E4">
-        <v>1.502288253087495</v>
+        <v>1.477723756182234</v>
       </c>
       <c r="F4">
-        <v>1.236763609039455</v>
+        <v>1.243611491964086</v>
       </c>
       <c r="G4">
-        <v>3.048902086110799</v>
+        <v>3.43999928924094</v>
       </c>
     </row>
     <row r="5">
@@ -487,16 +487,16 @@
         <v>50</v>
       </c>
       <c r="D5">
-        <v>1.853644123407109</v>
+        <v>1.920469703071417</v>
       </c>
       <c r="E5">
-        <v>1.819170720353188</v>
+        <v>1.912298278455281</v>
       </c>
       <c r="F5">
-        <v>1.594006121162643</v>
+        <v>1.56145901400501</v>
       </c>
       <c r="G5">
-        <v>2.515992045266861</v>
+        <v>2.585561161175659</v>
       </c>
     </row>
     <row r="6">
@@ -514,16 +514,16 @@
         <v>50</v>
       </c>
       <c r="D6">
-        <v>1.448077307078645</v>
+        <v>1.499074822127343</v>
       </c>
       <c r="E6">
-        <v>1.383350783945552</v>
+        <v>1.368491550057117</v>
       </c>
       <c r="F6">
-        <v>1.220639785246484</v>
+        <v>1.212843390018939</v>
       </c>
       <c r="G6">
-        <v>2.798928893985532</v>
+        <v>2.88531901204042</v>
       </c>
     </row>
     <row r="7">
@@ -541,16 +541,16 @@
         <v>50</v>
       </c>
       <c r="D7">
-        <v>1.5720963374543</v>
+        <v>1.722092511316225</v>
       </c>
       <c r="E7">
-        <v>1.514513243660158</v>
+        <v>1.643863586048358</v>
       </c>
       <c r="F7">
-        <v>1.16064134985917</v>
+        <v>1.153396596616052</v>
       </c>
       <c r="G7">
-        <v>2.637716579790983</v>
+        <v>2.682401614622326</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>50</v>
       </c>
       <c r="D8">
-        <v>1.476995971720132</v>
+        <v>1.489744086980394</v>
       </c>
       <c r="E8">
-        <v>1.454704808633997</v>
+        <v>1.504488000931946</v>
       </c>
       <c r="F8">
-        <v>1.267314418777337</v>
+        <v>1.201752488802483</v>
       </c>
       <c r="G8">
-        <v>1.803010337471874</v>
+        <v>1.815446933802622</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         <v>50</v>
       </c>
       <c r="D9">
-        <v>1.700821767281379</v>
+        <v>1.828251588954652</v>
       </c>
       <c r="E9">
-        <v>1.664804318580016</v>
+        <v>1.897675984787294</v>
       </c>
       <c r="F9">
-        <v>1.341750965907416</v>
+        <v>1.269409592134695</v>
       </c>
       <c r="G9">
-        <v>2.427025719244341</v>
+        <v>2.626178393264382</v>
       </c>
     </row>
     <row r="10">
@@ -622,16 +622,16 @@
         <v>50</v>
       </c>
       <c r="D10">
-        <v>1.765150429916495</v>
+        <v>1.892087547929423</v>
       </c>
       <c r="E10">
-        <v>1.58712888760718</v>
+        <v>1.683071779582402</v>
       </c>
       <c r="F10">
-        <v>1.379647773796419</v>
+        <v>1.374736781577682</v>
       </c>
       <c r="G10">
-        <v>3.207701354328157</v>
+        <v>3.26097429438029</v>
       </c>
     </row>
     <row r="11">
@@ -649,16 +649,16 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>1.612299616890415</v>
+        <v>1.625582299336528</v>
       </c>
       <c r="E11">
-        <v>1.429616884194682</v>
+        <v>1.44812503720108</v>
       </c>
       <c r="F11">
-        <v>1.161862056976177</v>
+        <v>1.187870052779872</v>
       </c>
       <c r="G11">
-        <v>2.779106459488364</v>
+        <v>2.718634383690239</v>
       </c>
     </row>
     <row r="12">
@@ -676,16 +676,16 @@
         <v>50</v>
       </c>
       <c r="D12">
-        <v>1.523930907762512</v>
+        <v>1.612351617953283</v>
       </c>
       <c r="E12">
-        <v>1.435079758225916</v>
+        <v>1.563301872876905</v>
       </c>
       <c r="F12">
-        <v>1.115018747939991</v>
+        <v>1.086096379514688</v>
       </c>
       <c r="G12">
-        <v>2.774653340206004</v>
+        <v>2.906218715641421</v>
       </c>
     </row>
     <row r="13">
@@ -703,16 +703,16 @@
         <v>50</v>
       </c>
       <c r="D13">
-        <v>1.638397945881749</v>
+        <v>1.09988480723676</v>
       </c>
       <c r="E13">
-        <v>1.650603449449017</v>
+        <v>1.099703903165247</v>
       </c>
       <c r="F13">
-        <v>1.392443042040213</v>
+        <v>1.06703132943667</v>
       </c>
       <c r="G13">
-        <v>1.790345256215909</v>
+        <v>1.159148435855952</v>
       </c>
     </row>
     <row r="14">
@@ -723,23 +723,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Peak_StO2_post_vascular_occlusion</t>
+          <t>rate_of_deoxygenation</t>
         </is>
       </c>
       <c r="C14">
         <v>50</v>
       </c>
       <c r="D14">
-        <v>1.638397945881749</v>
+        <v>1.09988480723676</v>
       </c>
       <c r="E14">
-        <v>1.650603449449017</v>
+        <v>1.099703903165247</v>
       </c>
       <c r="F14">
-        <v>1.392443042040213</v>
+        <v>1.06703132943667</v>
       </c>
       <c r="G14">
-        <v>1.790345256215909</v>
+        <v>1.159148435855952</v>
       </c>
     </row>
     <row r="15">
@@ -748,79 +748,59 @@
           <t>microvascular_function_model</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Microvascular_flox_index</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>50</v>
-      </c>
-      <c r="D15">
-        <v>1.062041447958839</v>
-      </c>
-      <c r="E15">
-        <v>1.047587858088247</v>
-      </c>
-      <c r="F15">
-        <v>1.000858682452947</v>
-      </c>
-      <c r="G15">
-        <v>1.261327697115924</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>microvascular_function_model</t>
+          <t>overall_model</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Perfused_vessel_density</t>
+          <t>Baseline_StO2_level</t>
         </is>
       </c>
       <c r="C16">
         <v>50</v>
       </c>
       <c r="D16">
-        <v>1.278776699842714</v>
+        <v>822.6889824259415</v>
       </c>
       <c r="E16">
-        <v>1.167442539394317</v>
+        <v>30.26939273480648</v>
       </c>
       <c r="F16">
-        <v>1.004160985030554</v>
+        <v>4.064207461623483</v>
       </c>
       <c r="G16">
-        <v>3.021494904365004</v>
+        <v>21269.4340861548</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>microvascular_function_model</t>
+          <t>overall_model</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Total_vessel_density</t>
+          <t>CRP</t>
         </is>
       </c>
       <c r="C17">
         <v>50</v>
       </c>
       <c r="D17">
-        <v>1.304691771107439</v>
+        <v>257.3292767815257</v>
       </c>
       <c r="E17">
-        <v>1.204618506152162</v>
+        <v>16.50043018313335</v>
       </c>
       <c r="F17">
-        <v>1.010252179526894</v>
+        <v>4.463770282412869</v>
       </c>
       <c r="G17">
-        <v>3.069064878010656</v>
+        <v>7929.749887858542</v>
       </c>
     </row>
     <row r="18">
@@ -831,23 +811,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Baseline_StO2_level</t>
+          <t>GCS</t>
         </is>
       </c>
       <c r="C18">
         <v>50</v>
       </c>
       <c r="D18">
-        <v>135.1711535688049</v>
+        <v>256.0469163737873</v>
       </c>
       <c r="E18">
-        <v>47.32812646817212</v>
+        <v>4.797046904665662</v>
       </c>
       <c r="F18">
-        <v>3.766783149253218</v>
+        <v>1.491794400235804</v>
       </c>
       <c r="G18">
-        <v>1250.324475000961</v>
+        <v>11653.55838739413</v>
       </c>
     </row>
     <row r="19">
@@ -858,23 +838,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CRP</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C19">
         <v>50</v>
       </c>
       <c r="D19">
-        <v>89.95249899064949</v>
+        <v>2124.801052818219</v>
       </c>
       <c r="E19">
-        <v>29.83567463876128</v>
+        <v>28.61637515419347</v>
       </c>
       <c r="F19">
-        <v>1.882118340950147</v>
+        <v>6.988381583444632</v>
       </c>
       <c r="G19">
-        <v>1135.073117935783</v>
+        <v>102084.081423376</v>
       </c>
     </row>
     <row r="20">
@@ -885,23 +865,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GCS</t>
+          <t>Lactate</t>
         </is>
       </c>
       <c r="C20">
         <v>50</v>
       </c>
       <c r="D20">
-        <v>34.98725970782893</v>
+        <v>714.2067525366162</v>
       </c>
       <c r="E20">
-        <v>12.39765808292802</v>
+        <v>34.89428772682248</v>
       </c>
       <c r="F20">
-        <v>3.194061346373741</v>
+        <v>6.505966840468595</v>
       </c>
       <c r="G20">
-        <v>545.9679979495978</v>
+        <v>22494.75371356454</v>
       </c>
     </row>
     <row r="21">
@@ -912,23 +892,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>MAP</t>
         </is>
       </c>
       <c r="C21">
         <v>50</v>
       </c>
       <c r="D21">
-        <v>109.8553577470581</v>
+        <v>646.371697365276</v>
       </c>
       <c r="E21">
-        <v>37.16208297732435</v>
+        <v>40.57114531421878</v>
       </c>
       <c r="F21">
-        <v>6.858100402444717</v>
+        <v>7.886133509947093</v>
       </c>
       <c r="G21">
-        <v>1839.120161403737</v>
+        <v>22711.34104585439</v>
       </c>
     </row>
     <row r="22">
@@ -939,23 +919,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lactate</t>
+          <t>Microvascular_flox_index</t>
         </is>
       </c>
       <c r="C22">
         <v>50</v>
       </c>
       <c r="D22">
-        <v>858.4485132979331</v>
+        <v>1031.848116214241</v>
       </c>
       <c r="E22">
-        <v>39.19550267420381</v>
+        <v>38.92037992566169</v>
       </c>
       <c r="F22">
-        <v>5.395376023773407</v>
+        <v>6.770482175694151</v>
       </c>
       <c r="G22">
-        <v>38408.33297177466</v>
+        <v>23840.09252564319</v>
       </c>
     </row>
     <row r="23">
@@ -966,23 +946,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>MRproADM</t>
         </is>
       </c>
       <c r="C23">
         <v>50</v>
       </c>
       <c r="D23">
-        <v>84.80552239798685</v>
+        <v>599.7122563354845</v>
       </c>
       <c r="E23">
-        <v>37.31532598158788</v>
+        <v>38.08242881645756</v>
       </c>
       <c r="F23">
-        <v>7.563321043321265</v>
+        <v>3.082212004467415</v>
       </c>
       <c r="G23">
-        <v>953.5400097284936</v>
+        <v>20267.71589761939</v>
       </c>
     </row>
     <row r="24">
@@ -993,23 +973,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Microvascular_flox_index</t>
+          <t>Procalcitonin</t>
         </is>
       </c>
       <c r="C24">
         <v>50</v>
       </c>
       <c r="D24">
-        <v>291.7449647036795</v>
+        <v>610.6198894120604</v>
       </c>
       <c r="E24">
-        <v>35.15437784424577</v>
+        <v>23.96999777012174</v>
       </c>
       <c r="F24">
-        <v>3.765474923744832</v>
+        <v>4.414264438505872</v>
       </c>
       <c r="G24">
-        <v>10361.75096995754</v>
+        <v>11276.87304753396</v>
       </c>
     </row>
     <row r="25">
@@ -1020,23 +1000,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MRproADM</t>
+          <t>rate_of_deoxygenation</t>
         </is>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25">
-        <v>901.5778346004037</v>
+        <v>336.209281350932</v>
       </c>
       <c r="E25">
-        <v>48.81063748316966</v>
+        <v>12.73459062448851</v>
       </c>
       <c r="F25">
-        <v>4.32976536903162</v>
+        <v>2.556917879292073</v>
       </c>
       <c r="G25">
-        <v>35833.87958722733</v>
+        <v>11406.55444360011</v>
       </c>
     </row>
     <row r="26">
@@ -1047,23 +1027,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Peak_StO2_post_vascular_occlusion</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C26">
         <v>50</v>
       </c>
       <c r="D26">
-        <v>82.01453599722591</v>
+        <v>570.2339906592599</v>
       </c>
       <c r="E26">
-        <v>39.51365413157465</v>
+        <v>38.79641007645653</v>
       </c>
       <c r="F26">
-        <v>5.391858779797016</v>
+        <v>3.279093368702146</v>
       </c>
       <c r="G26">
-        <v>706.1333787034682</v>
+        <v>11944.47920466178</v>
       </c>
     </row>
     <row r="27">
@@ -1074,23 +1054,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Perfused_vessel_density</t>
+          <t>SpO2</t>
         </is>
       </c>
       <c r="C27">
         <v>50</v>
       </c>
       <c r="D27">
-        <v>635.0942239579537</v>
+        <v>1450.178677982363</v>
       </c>
       <c r="E27">
-        <v>80.14251177224058</v>
+        <v>29.2763903785137</v>
       </c>
       <c r="F27">
-        <v>8.638619659716184</v>
+        <v>2.768962038848179</v>
       </c>
       <c r="G27">
-        <v>22467.54459623982</v>
+        <v>60569.96793276137</v>
       </c>
     </row>
     <row r="28">
@@ -1101,131 +1081,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Procalcitonin</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="C28">
         <v>50</v>
       </c>
       <c r="D28">
-        <v>333.3116786202985</v>
+        <v>509.4903886697898</v>
       </c>
       <c r="E28">
-        <v>42.77970003449217</v>
+        <v>25.12974869021984</v>
       </c>
       <c r="F28">
-        <v>2.482750447601582</v>
+        <v>7.337489302053122</v>
       </c>
       <c r="G28">
-        <v>10487.05137187948</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>overall_model</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>50</v>
-      </c>
-      <c r="D29">
-        <v>189.4396610753813</v>
-      </c>
-      <c r="E29">
-        <v>64.39769323917592</v>
-      </c>
-      <c r="F29">
-        <v>8.130739220424218</v>
-      </c>
-      <c r="G29">
-        <v>3449.854710218602</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>overall_model</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SpO2</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>50</v>
-      </c>
-      <c r="D30">
-        <v>80.79060288495108</v>
-      </c>
-      <c r="E30">
-        <v>37.00288251662057</v>
-      </c>
-      <c r="F30">
-        <v>7.914672679073322</v>
-      </c>
-      <c r="G30">
-        <v>810.6762919934713</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>overall_model</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>50</v>
-      </c>
-      <c r="D31">
-        <v>73.70098320019002</v>
-      </c>
-      <c r="E31">
-        <v>22.07433251373327</v>
-      </c>
-      <c r="F31">
-        <v>5.662440450591949</v>
-      </c>
-      <c r="G31">
-        <v>1497.711791552818</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>overall_model</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Total_vessel_density</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>50</v>
-      </c>
-      <c r="D32">
-        <v>134.5076189592667</v>
-      </c>
-      <c r="E32">
-        <v>33.3270357524955</v>
-      </c>
-      <c r="F32">
-        <v>6.252581630017509</v>
-      </c>
-      <c r="G32">
-        <v>2188.287100107471</v>
+        <v>13584.5560726087</v>
       </c>
     </row>
   </sheetData>
